--- a/output/pdf_financials_xlsx/CBLT.xlsx
+++ b/output/pdf_financials_xlsx/CBLT.xlsx
@@ -2295,7 +2295,7 @@
         <v>-0.556343</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.429665</v>
+        <v>-0.429665</v>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>-0.556343</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.429665</v>
+        <v>-0.429665</v>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>-0.556343</v>
       </c>
       <c r="Q403" s="5" t="n">
-        <v>0.429665</v>
+        <v>-0.429665</v>
       </c>
       <c r="R403" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CBLT.xlsx
+++ b/output/pdf_financials_xlsx/CBLT.xlsx
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.079989</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.021759</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.079989</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.021759</v>
@@ -41422,7 +41422,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E325" s="5" t="n">

--- a/output/pdf_financials_xlsx/CBLT.xlsx
+++ b/output/pdf_financials_xlsx/CBLT.xlsx
@@ -726,10 +726,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
@@ -906,13 +904,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P7" s="3" t="n">
+        <v>0.132</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>0</v>
@@ -994,10 +990,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>0</v>
@@ -1082,10 +1076,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
@@ -1170,13 +1162,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P10" s="3" t="n">
+        <v>0.132</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1350,10 +1340,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1438,10 +1426,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>-0</v>
@@ -1526,10 +1512,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
@@ -1614,10 +1598,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
@@ -1702,10 +1684,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P16" s="3" t="n">
+        <v>-0.981089</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0.038799</v>
@@ -1790,13 +1770,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P17" s="3" t="n">
+        <v>0.068416</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-2e-05</v>
+        <v>0.003074</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0</v>
@@ -2062,10 +2040,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P20" s="3" t="n">
+        <v>-0.912673</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0.038779</v>
@@ -2150,10 +2126,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0</v>
@@ -2238,10 +2212,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
@@ -2664,10 +2636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P27" s="3" t="n">
+        <v>-0.981089</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0.038799</v>
@@ -2752,10 +2722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2840,10 +2808,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P29" s="3" t="n">
+        <v>-0.981089</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0.038799</v>
@@ -3020,13 +2986,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P31" s="3" t="n">
+        <v>-6.97347539316005</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0.05154772030206964</v>
+        <v>7.922884610428103</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0</v>
@@ -7691,10 +7655,10 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.002218</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.001839</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -7703,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7717,16 +7681,16 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.002275</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.00518</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.003175</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.001701</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -8017,13 +7981,13 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.015139</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -9299,7 +9263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U512"/>
+  <dimension ref="A1:U562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -43727,7 +43691,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -45660,7 +45628,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -46662,7 +46634,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -47565,7 +47541,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -49862,7 +49842,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -50957,7 +50941,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -57694,10 +57682,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S488" s="5" t="n">
+        <v>-0.981089</v>
       </c>
       <c r="T488" s="5" t="n">
         <v>0.038799</v>
@@ -58522,7 +58508,11 @@
           <t>Income tax (recovery) $</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -58694,15 +58684,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S498" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T498" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S498" s="5" t="n">
+        <v>-0.068416</v>
+      </c>
+      <c r="T498" s="5" t="n">
+        <v>-0.003074</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
@@ -58900,15 +58886,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S500" s="5" t="n">
+        <v>-0.068416</v>
+      </c>
+      <c r="T500" s="5" t="n">
+        <v>-0.003074</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
@@ -59003,10 +58985,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S501" s="5" t="n">
+        <v>3.616</v>
       </c>
       <c r="T501" s="5" t="n">
         <v>3.681</v>
@@ -59102,10 +59082,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S502" s="5" t="n">
+        <v>0.002</v>
       </c>
       <c r="T502" s="5" t="n">
         <v>0.001</v>
@@ -59203,10 +59181,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S503" s="5" t="n">
+        <v>0.989</v>
       </c>
       <c r="T503" s="5" t="n">
         <v>1.165</v>
@@ -59302,10 +59278,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S504" s="5" t="n">
+        <v>0.034</v>
       </c>
       <c r="T504" s="5" t="n">
         <v>0.042</v>
@@ -59504,10 +59478,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S506" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S506" s="5" t="n">
+        <v>4.641</v>
       </c>
       <c r="T506" s="5" t="n">
         <v>4.889</v>
@@ -60007,10 +59979,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S511" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -60110,10 +60080,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S512" s="5" t="n">
+        <v>0.0127</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -60121,6 +60089,4996 @@
         </is>
       </c>
       <c r="U512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>incurred by the Company</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Property payments $</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S513" s="5" t="n">
+        <v>0.036986</v>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>incurred by the Company</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Claims maintenance</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S514" s="5" t="n">
+        <v>0.004156</v>
+      </c>
+      <c r="T514" s="5" t="n">
+        <v>0.018363</v>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>incurred by the Company</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Geological services</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S515" s="5" t="n">
+        <v>0.028026</v>
+      </c>
+      <c r="T515" s="5" t="n">
+        <v>0.023911</v>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>incurred by the Company</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Prospecting</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S516" s="5" t="n">
+        <v>0.018098</v>
+      </c>
+      <c r="T516" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>incurred by the Company</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S517" s="5" t="n">
+        <v>0.087266</v>
+      </c>
+      <c r="T517" s="5" t="n">
+        <v>0.046773</v>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>4.    INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Newpath Resources Inc. $</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S518" s="5" t="n">
+        <v>0.074892</v>
+      </c>
+      <c r="T518" s="5" t="n">
+        <v>0.017417</v>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>4.    INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>PowerStone Metals Corp.</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S519" s="5" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="T519" s="5" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>4.    INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Ciscom Corp.</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S520" s="5" t="n">
+        <v>0.110731</v>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>4.    INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>4.    INVESTMENTS total</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S521" s="5" t="n">
+        <v>0.204373</v>
+      </c>
+      <c r="T521" s="5" t="n">
+        <v>0.028667</v>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>$399,993.</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>23, 2023, and the payment date to June</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S522" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="T522" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>parties</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Management fees (i) $</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S523" s="5" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="T523" s="5" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>parties</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Share-based compensation (ii)</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T524" s="5" t="n">
+        <v>0.050019</v>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Number of Shares         Share Capital</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Balance May 31, 2023</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S525" s="5" t="n">
+        <v>4.355364</v>
+      </c>
+      <c r="T525" s="5" t="n">
+        <v>76.17707299999999</v>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Number of Shares         Share Capital</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Issued during the year</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S526" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T526" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>twenty-four months from the date of issue</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>There were no share issuances during the year ended May</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S527" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="T527" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Number of Options               Exercise Price</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Balance May 31, 2022</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S528" s="5" t="n">
+        <v>8e-08</v>
+      </c>
+      <c r="T528" s="5" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Number of Options               Exercise Price</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Cancelled or expired</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S529" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="T529" s="5" t="n">
+        <v>-0.609</v>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Number of Options               Exercise Price</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Balance May 31, 2023</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S530" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="T530" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Number of Options               Exercise Price</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Granted</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S531" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="T531" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Number of Options               Exercise Price</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Balance May 31, 2024</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S532" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="T532" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>1,000,000 1,000.000 0.05 August</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S533" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="T533" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>1,900,000 1,900,000 0.055 November</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S534" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="T534" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>100,000 100,000 0.05 April</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S535" s="5" t="n">
+        <v>0.002027</v>
+      </c>
+      <c r="T535" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2,150,000 2,150,000 0.05 September</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S536" s="5" t="n">
+        <v>0.002028</v>
+      </c>
+      <c r="T536" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>outstanding              Exercisable        Exercise price          Expiry date total</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S537" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T537" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>at grant   Exercise     interest   Expected    Volatility   Dividend</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>$ 0.025 $ 0.05 3.96% 5 years 172% 0% 10, 2023</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S538" s="5" t="n">
+        <v>0.002028</v>
+      </c>
+      <c r="T538" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Exercise         Expiry         Outstanding       Outstanding</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Price Date May 31, 2023 May</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S539" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="T539" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Exercise         Expiry         Outstanding       Outstanding</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Private placement $0.06 December 27, 2025</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S540" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Exercise         Expiry         Outstanding       Outstanding</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Private placement $0.06 January 30, 2026</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S541" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Opening Balance $</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S542" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T542" s="5" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Adjustment to provision</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S543" s="5" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="T543" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Interest accretion</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T544" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Reversal of previous provision</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T545" s="5" t="n">
+        <v>-0.224231</v>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Transfer of provision to accounts payable</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T546" s="5" t="n">
+        <v>-0.015769</v>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Closing Balance May 31 $</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S547" s="5" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="T547" s="5" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>11.   PROVISION FOR INDEMNIFICATION OF FLOW-THROUGH SUBSCRIBERS</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>placements for which flow-through share proceeds had been received by the Company and then renounced to subscribers effective December</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S548" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="T548" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Expected income tax recovery at the statutory</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Expected income tax recovery at the statutory tax rate</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S549" s="5" t="n">
+        <v>-0.259989</v>
+      </c>
+      <c r="T549" s="5" t="n">
+        <v>0.009462</v>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Expected income tax recovery at the statutory</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T550" s="5" t="n">
+        <v>0.013255</v>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair value through profit and loss unrealized</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S551" s="5" t="n">
+        <v>0.037081</v>
+      </c>
+      <c r="T551" s="5" t="n">
+        <v>0.017218</v>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Realized loss (gain) on sale of investments</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr"/>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S552" s="5" t="n">
+        <v>0.110243</v>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Gain on sale of mineral properties</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S553" s="5" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="T553" s="5" t="n">
+        <v>-0.0477</v>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S554" s="5" t="n">
+        <v>-0.000764</v>
+      </c>
+      <c r="T554" s="5" t="n">
+        <v>-0.000294</v>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr"/>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S555" s="5" t="n">
+        <v>0.024126</v>
+      </c>
+      <c r="T555" s="5" t="n">
+        <v>-0.009115</v>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Benefit of tax losses not recognized</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr"/>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S556" s="5" t="n">
+        <v>0.09460300000000001</v>
+      </c>
+      <c r="T556" s="5" t="n">
+        <v>0.017174</v>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Benefit of deferred tax assets recognized</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Flow-through premium</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S558" s="5" t="n">
+        <v>-0.068416</v>
+      </c>
+      <c r="T558" s="5" t="n">
+        <v>-0.003074</v>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Loss (gain) on financial instruments held at fair</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Income tax (recovery) $</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S559" s="5" t="n">
+        <v>-0.068416</v>
+      </c>
+      <c r="T559" s="5" t="n">
+        <v>-0.003074</v>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>following</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Marketable securities $</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>statements.</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Capital losses carried forward</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Balance at May 31,</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S562" s="5" t="n">
+        <v>0.038516</v>
+      </c>
+      <c r="T562" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="U562" t="inlineStr">
         <is>
           <t>-</t>
         </is>
